--- a/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98867634-3111-439A-B3ED-12740A6F716B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DD32BD-1FA0-4D02-8B60-9299CF7FCA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,15 +33,9 @@
     <t>DONE</t>
   </si>
   <si>
-    <t>Machine Learning Checklist</t>
-  </si>
-  <si>
     <t>Ensure the training dataset is stable and has been reviewed and critiqued by stakeholders.</t>
   </si>
   <si>
-    <t>Ensure the training dataset has been quality assured in at least 10 different ways.</t>
-  </si>
-  <si>
     <t>Log the total number of rows, class distribution, and missing values for each column.</t>
   </si>
   <si>
@@ -54,14 +48,49 @@
     <t>Set random seeds for all non-deterministic processes to ensure reproducibility.</t>
   </si>
   <si>
-    <t>Perform the train-test split correctly before fitting any preprocessing or modelling components.</t>
-  </si>
-  <si>
     <t>Ensure there is no data leakage throughout the pipeline.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Implement an appropriate imputation strategy rather than simply using </t>
+    <t>Fit imputation models using only the training data and apply them to both the training and test datasets.</t>
+  </si>
+  <si>
+    <t>Perform K-fold cross-validation on the training dataset.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement and validate a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>predict()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> function for inference on new data.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ensure the training dataset has undergone comprehensive quality assurance (e.g., at least 10 different validation checks).</t>
+  </si>
+  <si>
+    <t>Document all modelling assumptions.</t>
+  </si>
+  <si>
+    <t>Perform the train-test split before fitting any preprocessing, feature engineering, imputation, or modelling components.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement an appropriate imputation strategy instead of relying on </t>
     </r>
     <r>
       <rPr>
@@ -102,84 +131,47 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>) when fitting imputation models in supervised learning tasks.</t>
-    </r>
-  </si>
-  <si>
-    <t>Fit imputation models using only the training data and apply them to both the training and test datasets.</t>
-  </si>
-  <si>
-    <t>Fit scalers and other preprocessing transformations on the training data only and apply them to both the training and test datasets.</t>
-  </si>
-  <si>
-    <t>Follow a well-defined pipeline: transformations → train-test split → preprocessing for imputation → imputation → post-imputation preprocessing → model training → post-training evaluation.</t>
-  </si>
-  <si>
-    <t>Apply upsampling or resampling only to the training data and never to the test data.</t>
-  </si>
-  <si>
-    <t>Perform K-fold cross-validation on the training dataset.</t>
-  </si>
-  <si>
-    <t>Use appropriate evaluation metrics for imbalanced classification problems, including F1-score and Matthews Correlation Coefficient (MCC).</t>
-  </si>
-  <si>
-    <t>Compute the Brier score when evaluating models that produce probability estimates.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement and validate a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>predict()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> function for inference on new data.</t>
-    </r>
-  </si>
-  <si>
-    <t>Provide a dashboard or interface for testing and interacting with the model.</t>
-  </si>
-  <si>
-    <t>Implement a mechanism to monitor model performance in production.</t>
-  </si>
-  <si>
-    <t>Implement a process to retrain or update the model when performance deteriorates or data changes.</t>
-  </si>
-  <si>
-    <t>categorical columns have been made one-hot encoding</t>
-  </si>
-  <si>
-    <t>assumptions are listed</t>
+      <t>) when fitting imputation models for supervised learning tasks.</t>
+    </r>
+  </si>
+  <si>
+    <t>Convert categorical variables using one-hot encoding where appropriate.</t>
+  </si>
+  <si>
+    <t>Drop one reference level during one-hot encoding where required to avoid multicollinearity.</t>
+  </si>
+  <si>
+    <t>Fit feature scalers and other preprocessing transformations using only the training data and apply them to both the training and test datasets.</t>
+  </si>
+  <si>
+    <t>Follow a consistent pipeline: feature engineering → train-test split → pre-imputation preprocessing → imputation → post-imputation preprocessing → resampling (training data only) → model training → cross-validation → evaluation → final testing.</t>
+  </si>
+  <si>
+    <t>Apply upsampling, downsampling, or other resampling techniques only to the training data.</t>
+  </si>
+  <si>
+    <t>Use evaluation metrics appropriate for the problem, including F1-score and Matthews Correlation Coefficient (MCC) for imbalanced classification.</t>
+  </si>
+  <si>
+    <t>Compute the Brier score for models that produce probability estimates.</t>
+  </si>
+  <si>
+    <t>Provide a dashboard, interface, or API for testing and interacting with the model.</t>
+  </si>
+  <si>
+    <t>Monitor model performance in production.</t>
+  </si>
+  <si>
+    <t>Implement a retraining strategy to update the model when performance degrades or data distributions change.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -211,13 +203,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -520,7 +509,7 @@
   <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="65.7265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="73.81640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -531,186 +520,192 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="23.5">
+    <row r="2" spans="1:2" ht="29">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="3"/>
+      <c r="A3" s="2"/>
     </row>
     <row r="4" spans="1:2" ht="29">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:2" ht="29">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" ht="29">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3"/>
-    </row>
-    <row r="8" spans="1:2" ht="29">
-      <c r="A8" s="3" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="3" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:2" ht="29">
+      <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="3" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:2" ht="29">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:2" ht="29">
-      <c r="A14" s="3" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:1" ht="29">
+      <c r="A20" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1" ht="29">
+      <c r="A22" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:1" ht="29">
+      <c r="A24" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:2" ht="29">
-      <c r="A16" s="3" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" spans="1:1" ht="29">
+      <c r="A28" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="2"/>
+    </row>
+    <row r="30" spans="1:1" ht="29">
+      <c r="A30" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="2"/>
+    </row>
+    <row r="32" spans="1:1" ht="58">
+      <c r="A32" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" spans="1:1" ht="29">
+      <c r="A34" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="3"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="3" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:1" ht="29">
+      <c r="A38" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="2"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="2"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="3"/>
-    </row>
-    <row r="20" spans="1:1" ht="29">
-      <c r="A20" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="3"/>
-    </row>
-    <row r="22" spans="1:1" ht="29">
-      <c r="A22" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="3"/>
-    </row>
-    <row r="24" spans="1:1" ht="29">
-      <c r="A24" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="3"/>
-    </row>
-    <row r="26" spans="1:1" ht="29">
-      <c r="A26" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="3"/>
-    </row>
-    <row r="28" spans="1:1" ht="43.5">
-      <c r="A28" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="3"/>
-    </row>
-    <row r="30" spans="1:1" ht="29">
-      <c r="A30" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="3"/>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="3"/>
-    </row>
-    <row r="34" spans="1:1" ht="29">
-      <c r="A34" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="3"/>
-    </row>
-    <row r="36" spans="1:1" ht="29">
-      <c r="A36" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="3"/>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="3"/>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="3"/>
+      <c r="A43" s="2"/>
     </row>
     <row r="44" spans="1:1" ht="29">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="2" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2"/>
+    </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
+    <row r="47" spans="1:1">
+      <c r="A47" s="2"/>
+    </row>
+    <row r="48" spans="1:1" ht="29">
+      <c r="A48" s="2" t="s">
         <v>25</v>
       </c>
     </row>
